--- a/RL/results_rotations_film_a.xlsx
+++ b/RL/results_rotations_film_a.xlsx
@@ -566,49 +566,49 @@
         <v>76.34999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>10011</v>
+        <v>9563</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>77.55</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.57</v>
+        <v>2.02</v>
       </c>
       <c r="L2" t="b">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>9760</v>
+        <v>9563</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>76.34999999999999</v>
+        <v>77.55</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="b">
         <v>0</v>
       </c>
       <c r="R2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>135.7</v>
+        <v>193.4</v>
       </c>
       <c r="V2" t="n">
-        <v>163.65</v>
+        <v>162.45</v>
       </c>
     </row>
     <row r="3">
@@ -636,49 +636,49 @@
         <v>76.34999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>10011</v>
+        <v>9563</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>77.55</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.57</v>
+        <v>2.02</v>
       </c>
       <c r="L3" t="b">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>9760</v>
+        <v>9563</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>76.34999999999999</v>
+        <v>77.55</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q3" t="b">
         <v>0</v>
       </c>
       <c r="R3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>75.09999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="V3" t="n">
-        <v>223.65</v>
+        <v>222.45</v>
       </c>
     </row>
     <row r="4">
@@ -706,49 +706,49 @@
         <v>76.34999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>9760</v>
+        <v>9563</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>76.34999999999999</v>
+        <v>77.55</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="L4" t="b">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>9760</v>
+        <v>9563</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>76.34999999999999</v>
+        <v>77.55</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
       <c r="R4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>67.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>999923.65</v>
+        <v>999922.45</v>
       </c>
     </row>
   </sheetData>
@@ -815,22 +815,22 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-2.57</v>
+        <v>2.02</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>163.65</v>
+        <v>162.45</v>
       </c>
     </row>
     <row r="3">
@@ -841,22 +841,22 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>-2.57</v>
+        <v>2.02</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>223.65</v>
+        <v>222.45</v>
       </c>
     </row>
     <row r="4">
@@ -867,22 +867,22 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>999923.65</v>
+        <v>999922.45</v>
       </c>
     </row>
   </sheetData>
